--- a/Atribucion Nueva/Ventas.xlsx
+++ b/Atribucion Nueva/Ventas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://provenzal-my.sharepoint.com/personal/analistaseniordata_provenzal_com_co/Documents/Escritorio/Analisis-de-datos/Atribucion Nueva/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_332D10BCD3505131AC4C13B1545ED87656CDBE54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EA11CB0-7CE0-48D8-A4E0-7E22B87CEA28}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_332D10BCD3505131AC4C13B1545ED87656CDBE54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F55E7981-B225-436A-BD88-E582C3DBEDB3}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-156" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -353,7 +353,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -411,7 +411,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,7 +717,9 @@
   <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
